--- a/ml/data/raw_transactions_user3.xlsx
+++ b/ml/data/raw_transactions_user3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\朱冠勳\Desktop\專題相關\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\朱冠勳\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533409A1-63D4-49FC-8716-45EB86FF01DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C557977-EFD2-4FAE-8E21-66461F3F8D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{1C98EAD0-93C5-43B6-8C07-C5C95E622A87}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="6">
   <si>
     <t>time_stamp</t>
   </si>
@@ -51,6 +51,10 @@
   </si>
   <si>
     <t>Expense</t>
+  </si>
+  <si>
+    <t>Income</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -440,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1C43C9E-3F29-4916-A2FE-A980B368D834}">
-  <dimension ref="A1:D315"/>
+  <dimension ref="A1:D324"/>
   <sheetFormatPr defaultRowHeight="16.149999999999999" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.46484375" customWidth="1"/>
@@ -586,17 +590,17 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
-        <v>46013</v>
+        <v>46023</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>50</v>
+        <v>10000</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>-2683</v>
+        <v>7367</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
@@ -607,11 +611,11 @@
         <v>4</v>
       </c>
       <c r="C11">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>-2908</v>
+        <v>7317</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
@@ -622,26 +626,26 @@
         <v>4</v>
       </c>
       <c r="C12">
-        <v>135</v>
+        <v>225</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>-3043</v>
+        <v>7092</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
-        <v>46012</v>
+        <v>46013</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
       </c>
       <c r="C13">
-        <v>248</v>
+        <v>135</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>-3291</v>
+        <v>6957</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
@@ -652,26 +656,26 @@
         <v>4</v>
       </c>
       <c r="C14">
-        <v>75</v>
+        <v>248</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>-3366</v>
+        <v>6709</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
-        <v>46007</v>
+        <v>46012</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
       </c>
       <c r="C15">
-        <v>569</v>
+        <v>75</v>
       </c>
       <c r="D15">
         <f t="shared" si="0"/>
-        <v>-3935</v>
+        <v>6634</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
@@ -682,26 +686,26 @@
         <v>4</v>
       </c>
       <c r="C16">
-        <v>120</v>
+        <v>569</v>
       </c>
       <c r="D16">
         <f t="shared" si="0"/>
-        <v>-4055</v>
+        <v>6065</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
       </c>
       <c r="C17">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="D17">
         <f t="shared" si="0"/>
-        <v>-4275</v>
+        <v>5945</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
@@ -712,41 +716,41 @@
         <v>4</v>
       </c>
       <c r="C18">
-        <v>64</v>
+        <v>220</v>
       </c>
       <c r="D18">
         <f t="shared" si="0"/>
-        <v>-4339</v>
+        <v>5725</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B19" t="s">
         <v>4</v>
       </c>
       <c r="C19">
-        <v>150</v>
+        <v>64</v>
       </c>
       <c r="D19">
         <f t="shared" si="0"/>
-        <v>-4489</v>
+        <v>5661</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B20" t="s">
         <v>4</v>
       </c>
       <c r="C20">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D20">
         <f t="shared" si="0"/>
-        <v>-4629</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
@@ -757,11 +761,11 @@
         <v>4</v>
       </c>
       <c r="C21">
-        <v>596</v>
+        <v>140</v>
       </c>
       <c r="D21">
         <f t="shared" si="0"/>
-        <v>-5225</v>
+        <v>5371</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
@@ -772,26 +776,26 @@
         <v>4</v>
       </c>
       <c r="C22">
-        <v>160</v>
+        <v>596</v>
       </c>
       <c r="D22">
         <f t="shared" si="0"/>
-        <v>-5385</v>
+        <v>4775</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B23" t="s">
         <v>4</v>
       </c>
       <c r="C23">
-        <v>310</v>
+        <v>160</v>
       </c>
       <c r="D23">
         <f t="shared" si="0"/>
-        <v>-5695</v>
+        <v>4615</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
@@ -802,26 +806,26 @@
         <v>4</v>
       </c>
       <c r="C24">
-        <v>165</v>
+        <v>310</v>
       </c>
       <c r="D24">
         <f t="shared" si="0"/>
-        <v>-5860</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B25" t="s">
         <v>4</v>
       </c>
       <c r="C25">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="D25">
         <f t="shared" si="0"/>
-        <v>-5985</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
@@ -832,41 +836,41 @@
         <v>4</v>
       </c>
       <c r="C26">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D26">
         <f t="shared" si="0"/>
-        <v>-6120</v>
+        <v>4015</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B27" t="s">
         <v>4</v>
       </c>
       <c r="C27">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="D27">
         <f t="shared" si="0"/>
-        <v>-6245</v>
+        <v>3880</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="2">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B28" t="s">
         <v>4</v>
       </c>
       <c r="C28">
-        <v>185</v>
+        <v>125</v>
       </c>
       <c r="D28">
         <f t="shared" si="0"/>
-        <v>-6430</v>
+        <v>3755</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
@@ -877,11 +881,11 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <v>45</v>
+        <v>185</v>
       </c>
       <c r="D29">
         <f t="shared" si="0"/>
-        <v>-6475</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
@@ -892,31 +896,31 @@
         <v>4</v>
       </c>
       <c r="C30">
-        <v>265</v>
+        <v>45</v>
       </c>
       <c r="D30">
         <f t="shared" si="0"/>
-        <v>-6740</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B31" t="s">
         <v>4</v>
       </c>
       <c r="C31">
-        <v>100</v>
+        <v>265</v>
       </c>
       <c r="D31">
         <f t="shared" si="0"/>
-        <v>-6840</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
@@ -926,7 +930,7 @@
       </c>
       <c r="D32">
         <f t="shared" si="0"/>
-        <v>-6940</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
@@ -941,112 +945,112 @@
       </c>
       <c r="D33">
         <f t="shared" si="0"/>
-        <v>-7040</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
       </c>
       <c r="C34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D34">
         <f t="shared" si="0"/>
-        <v>-7160</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B35" t="s">
         <v>4</v>
       </c>
       <c r="C35">
-        <v>340</v>
+        <v>120</v>
       </c>
       <c r="D35">
         <f t="shared" si="0"/>
-        <v>-7500</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B36" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36">
-        <v>350</v>
+        <v>10000</v>
       </c>
       <c r="D36">
         <f t="shared" si="0"/>
-        <v>-7850</v>
+        <v>12840</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="B37" t="s">
         <v>4</v>
       </c>
       <c r="C37">
-        <v>180</v>
+        <v>340</v>
       </c>
       <c r="D37">
         <f t="shared" si="0"/>
-        <v>-8030</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="B38" t="s">
         <v>4</v>
       </c>
       <c r="C38">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="D38">
         <f t="shared" si="0"/>
-        <v>-8230</v>
+        <v>12150</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
-        <v>45987</v>
+        <v>45988</v>
       </c>
       <c r="B39" t="s">
         <v>4</v>
       </c>
       <c r="C39">
-        <v>64</v>
+        <v>180</v>
       </c>
       <c r="D39">
         <f t="shared" si="0"/>
-        <v>-8294</v>
+        <v>11970</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
-        <v>45987</v>
+        <v>45988</v>
       </c>
       <c r="B40" t="s">
         <v>4</v>
       </c>
       <c r="C40">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="D40">
         <f t="shared" si="0"/>
-        <v>-8372</v>
+        <v>11770</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
@@ -1057,41 +1061,41 @@
         <v>4</v>
       </c>
       <c r="C41">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="D41">
         <f t="shared" si="0"/>
-        <v>-8502</v>
+        <v>11706</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B42" t="s">
         <v>4</v>
       </c>
       <c r="C42">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="D42">
         <f t="shared" si="0"/>
-        <v>-8632</v>
+        <v>11628</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B43" t="s">
         <v>4</v>
       </c>
       <c r="C43">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="D43">
         <f t="shared" si="0"/>
-        <v>-8682</v>
+        <v>11498</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
@@ -1102,56 +1106,56 @@
         <v>4</v>
       </c>
       <c r="C44">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D44">
         <f t="shared" si="0"/>
-        <v>-8807</v>
+        <v>11368</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="2">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B45" t="s">
         <v>4</v>
       </c>
       <c r="C45">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="D45">
         <f t="shared" si="0"/>
-        <v>-8900</v>
+        <v>11318</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
-        <v>45984</v>
+        <v>45986</v>
       </c>
       <c r="B46" t="s">
         <v>4</v>
       </c>
       <c r="C46">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="D46">
         <f t="shared" si="0"/>
-        <v>-8989</v>
+        <v>11193</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="2">
-        <v>45984</v>
+        <v>45985</v>
       </c>
       <c r="B47" t="s">
         <v>4</v>
       </c>
       <c r="C47">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="D47">
         <f t="shared" si="0"/>
-        <v>-9024</v>
+        <v>11100</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.45">
@@ -1162,11 +1166,11 @@
         <v>4</v>
       </c>
       <c r="C48">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="D48">
         <f t="shared" si="0"/>
-        <v>-9140</v>
+        <v>11011</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
@@ -1177,41 +1181,41 @@
         <v>4</v>
       </c>
       <c r="C49">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="D49">
         <f t="shared" si="0"/>
-        <v>-9219</v>
+        <v>10976</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
-        <v>45981</v>
+        <v>45984</v>
       </c>
       <c r="B50" t="s">
         <v>4</v>
       </c>
       <c r="C50">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="D50">
         <f t="shared" si="0"/>
-        <v>-9319</v>
+        <v>10860</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
-        <v>45981</v>
+        <v>45984</v>
       </c>
       <c r="B51" t="s">
         <v>4</v>
       </c>
       <c r="C51">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D51">
         <f t="shared" si="0"/>
-        <v>-9394</v>
+        <v>10781</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.45">
@@ -1222,11 +1226,11 @@
         <v>4</v>
       </c>
       <c r="C52">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D52">
         <f t="shared" si="0"/>
-        <v>-9594</v>
+        <v>10681</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.45">
@@ -1237,136 +1241,136 @@
         <v>4</v>
       </c>
       <c r="C53">
-        <v>300</v>
+        <v>75</v>
       </c>
       <c r="D53">
         <f t="shared" si="0"/>
-        <v>-9894</v>
+        <v>10606</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B54" t="s">
         <v>4</v>
       </c>
       <c r="C54">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="D54">
         <f t="shared" si="0"/>
-        <v>-10014</v>
+        <v>10406</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" s="2">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B55" t="s">
         <v>4</v>
       </c>
       <c r="C55">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="D55">
         <f t="shared" si="0"/>
-        <v>-10264</v>
+        <v>10106</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" s="2">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B56" t="s">
         <v>4</v>
       </c>
       <c r="C56">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D56">
         <f t="shared" si="0"/>
-        <v>-10389</v>
+        <v>9986</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B57" t="s">
         <v>4</v>
       </c>
       <c r="C57">
-        <v>39</v>
+        <v>250</v>
       </c>
       <c r="D57">
         <f t="shared" si="0"/>
-        <v>-10428</v>
+        <v>9736</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B58" t="s">
         <v>4</v>
       </c>
       <c r="C58">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="D58">
         <f t="shared" si="0"/>
-        <v>-10528</v>
+        <v>9611</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" s="2">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B59" t="s">
         <v>4</v>
       </c>
       <c r="C59">
-        <v>295</v>
+        <v>39</v>
       </c>
       <c r="D59">
         <f t="shared" si="0"/>
-        <v>-10823</v>
+        <v>9572</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B60" t="s">
         <v>4</v>
       </c>
       <c r="C60">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="D60">
         <f t="shared" si="0"/>
-        <v>-11073</v>
+        <v>9472</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B61" t="s">
         <v>4</v>
       </c>
       <c r="C61">
-        <v>110</v>
+        <v>295</v>
       </c>
       <c r="D61">
         <f t="shared" si="0"/>
-        <v>-11183</v>
+        <v>9177</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62" s="2">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B62" t="s">
         <v>4</v>
@@ -1376,97 +1380,97 @@
       </c>
       <c r="D62">
         <f t="shared" si="0"/>
-        <v>-11433</v>
+        <v>8927</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63" s="2">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B63" t="s">
         <v>4</v>
       </c>
       <c r="C63">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="D63">
         <f t="shared" si="0"/>
-        <v>-11663</v>
+        <v>8817</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" s="2">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B64" t="s">
         <v>4</v>
       </c>
       <c r="C64">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="D64">
         <f t="shared" si="0"/>
-        <v>-11718</v>
+        <v>8567</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" s="2">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B65" t="s">
         <v>4</v>
       </c>
       <c r="C65">
-        <v>125</v>
+        <v>230</v>
       </c>
       <c r="D65">
         <f t="shared" si="0"/>
-        <v>-11843</v>
+        <v>8337</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
-        <v>45969</v>
+        <v>45972</v>
       </c>
       <c r="B66" t="s">
         <v>4</v>
       </c>
       <c r="C66">
-        <v>2190</v>
+        <v>55</v>
       </c>
       <c r="D66">
         <f t="shared" si="0"/>
-        <v>-14033</v>
+        <v>8282</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B67" t="s">
         <v>4</v>
       </c>
       <c r="C67">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D67">
         <f t="shared" ref="D67:D130" si="1">IF(B67="Income",D66+C67,D66-C67)</f>
-        <v>-14153</v>
+        <v>8157</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
-        <v>45968</v>
+        <v>45969</v>
       </c>
       <c r="B68" t="s">
         <v>4</v>
       </c>
       <c r="C68">
-        <v>80</v>
+        <v>2190</v>
       </c>
       <c r="D68">
         <f t="shared" si="1"/>
-        <v>-14233</v>
+        <v>5967</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
@@ -1477,71 +1481,71 @@
         <v>4</v>
       </c>
       <c r="C69">
-        <v>1339</v>
+        <v>120</v>
       </c>
       <c r="D69">
         <f t="shared" si="1"/>
-        <v>-15572</v>
+        <v>5847</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" s="2">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B70" t="s">
         <v>4</v>
       </c>
       <c r="C70">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="D70">
         <f t="shared" si="1"/>
-        <v>-15690</v>
+        <v>5767</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" s="2">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B71" t="s">
         <v>4</v>
       </c>
       <c r="C71">
-        <v>700</v>
+        <v>1339</v>
       </c>
       <c r="D71">
         <f t="shared" si="1"/>
-        <v>-16390</v>
+        <v>4428</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" s="2">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B72" t="s">
         <v>4</v>
       </c>
       <c r="C72">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="D72">
         <f t="shared" si="1"/>
-        <v>-16490</v>
+        <v>4310</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" s="2">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B73" t="s">
         <v>4</v>
       </c>
       <c r="C73">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="D73">
         <f t="shared" si="1"/>
-        <v>-16590</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
@@ -1552,116 +1556,116 @@
         <v>4</v>
       </c>
       <c r="C74">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="D74">
         <f t="shared" si="1"/>
-        <v>-16720</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" s="2">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B75" t="s">
         <v>4</v>
       </c>
       <c r="C75">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D75">
         <f t="shared" si="1"/>
-        <v>-17020</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" s="2">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B76" t="s">
         <v>4</v>
       </c>
       <c r="C76">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="D76">
         <f t="shared" si="1"/>
-        <v>-17200</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77" s="2">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B77" t="s">
         <v>4</v>
       </c>
       <c r="C77">
-        <v>130</v>
+        <v>300</v>
       </c>
       <c r="D77">
         <f t="shared" si="1"/>
-        <v>-17330</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B78" t="s">
         <v>4</v>
       </c>
       <c r="C78">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D78">
         <f t="shared" si="1"/>
-        <v>-17520</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" s="2">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B79" t="s">
         <v>4</v>
       </c>
       <c r="C79">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="D79">
         <f t="shared" si="1"/>
-        <v>-17730</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80" s="2">
-        <v>45960</v>
+        <v>45962</v>
       </c>
       <c r="B80" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C80">
-        <v>163</v>
+        <v>10000</v>
       </c>
       <c r="D80">
         <f t="shared" si="1"/>
-        <v>-17893</v>
+        <v>12670</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" s="2">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B81" t="s">
         <v>4</v>
       </c>
       <c r="C81">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="D81">
         <f t="shared" si="1"/>
-        <v>-18063</v>
+        <v>12480</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.45">
@@ -1672,241 +1676,241 @@
         <v>4</v>
       </c>
       <c r="C82">
-        <v>550</v>
+        <v>210</v>
       </c>
       <c r="D82">
         <f t="shared" si="1"/>
-        <v>-18613</v>
+        <v>12270</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" s="2">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B83" t="s">
         <v>4</v>
       </c>
       <c r="C83">
-        <v>38</v>
+        <v>163</v>
       </c>
       <c r="D83">
         <f t="shared" si="1"/>
-        <v>-18651</v>
+        <v>12107</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" s="2">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B84" t="s">
         <v>4</v>
       </c>
       <c r="C84">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D84">
         <f t="shared" si="1"/>
-        <v>-18816</v>
+        <v>11937</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" s="2">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B85" t="s">
         <v>4</v>
       </c>
       <c r="C85">
-        <v>68</v>
+        <v>550</v>
       </c>
       <c r="D85">
         <f t="shared" si="1"/>
-        <v>-18884</v>
+        <v>11387</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B86" t="s">
         <v>4</v>
       </c>
       <c r="C86">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="D86">
         <f t="shared" si="1"/>
-        <v>-18984</v>
+        <v>11349</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B87" t="s">
         <v>4</v>
       </c>
       <c r="C87">
-        <v>89</v>
+        <v>165</v>
       </c>
       <c r="D87">
         <f t="shared" si="1"/>
-        <v>-19073</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" s="2">
-        <v>45954</v>
+        <v>45959</v>
       </c>
       <c r="B88" t="s">
         <v>4</v>
       </c>
       <c r="C88">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="D88">
         <f t="shared" si="1"/>
-        <v>-19198</v>
+        <v>11116</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="B89" t="s">
         <v>4</v>
       </c>
       <c r="C89">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D89">
         <f t="shared" si="1"/>
-        <v>-19313</v>
+        <v>11016</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="B90" t="s">
         <v>4</v>
       </c>
       <c r="C90">
-        <v>285</v>
+        <v>89</v>
       </c>
       <c r="D90">
         <f t="shared" si="1"/>
-        <v>-19598</v>
+        <v>10927</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" s="2">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B91" t="s">
         <v>4</v>
       </c>
       <c r="C91">
-        <v>603</v>
+        <v>125</v>
       </c>
       <c r="D91">
         <f t="shared" si="1"/>
-        <v>-20201</v>
+        <v>10802</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" s="2">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B92" t="s">
         <v>4</v>
       </c>
       <c r="C92">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="D92">
         <f t="shared" si="1"/>
-        <v>-20226</v>
+        <v>10687</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" s="2">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B93" t="s">
         <v>4</v>
       </c>
       <c r="C93">
-        <v>115</v>
+        <v>285</v>
       </c>
       <c r="D93">
         <f t="shared" si="1"/>
-        <v>-20341</v>
+        <v>10402</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" s="2">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B94" t="s">
         <v>4</v>
       </c>
       <c r="C94">
-        <v>94</v>
+        <v>603</v>
       </c>
       <c r="D94">
         <f t="shared" si="1"/>
-        <v>-20435</v>
+        <v>9799</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95" s="2">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B95" t="s">
         <v>4</v>
       </c>
       <c r="C95">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="D95">
         <f t="shared" si="1"/>
-        <v>-20535</v>
+        <v>9774</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96" s="2">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B96" t="s">
         <v>4</v>
       </c>
       <c r="C96">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D96">
         <f t="shared" si="1"/>
-        <v>-20660</v>
+        <v>9659</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97" s="2">
-        <v>45949</v>
+        <v>45952</v>
       </c>
       <c r="B97" t="s">
         <v>4</v>
       </c>
       <c r="C97">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="D97">
         <f t="shared" si="1"/>
-        <v>-20776</v>
+        <v>9565</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A98" s="2">
-        <v>45949</v>
+        <v>45951</v>
       </c>
       <c r="B98" t="s">
         <v>4</v>
@@ -1916,142 +1920,142 @@
       </c>
       <c r="D98">
         <f t="shared" si="1"/>
-        <v>-20876</v>
+        <v>9465</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99" s="2">
-        <v>45949</v>
+        <v>45950</v>
       </c>
       <c r="B99" t="s">
         <v>4</v>
       </c>
       <c r="C99">
-        <v>365</v>
+        <v>125</v>
       </c>
       <c r="D99">
         <f t="shared" si="1"/>
-        <v>-21241</v>
+        <v>9340</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" s="2">
-        <v>45947</v>
+        <v>45949</v>
       </c>
       <c r="B100" t="s">
         <v>4</v>
       </c>
       <c r="C100">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="D100">
         <f t="shared" si="1"/>
-        <v>-21401</v>
+        <v>9224</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101" s="2">
-        <v>45947</v>
+        <v>45949</v>
       </c>
       <c r="B101" t="s">
         <v>4</v>
       </c>
       <c r="C101">
-        <v>340</v>
+        <v>100</v>
       </c>
       <c r="D101">
         <f t="shared" si="1"/>
-        <v>-21741</v>
+        <v>9124</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A102" s="2">
-        <v>45947</v>
+        <v>45949</v>
       </c>
       <c r="B102" t="s">
         <v>4</v>
       </c>
       <c r="C102">
-        <v>150</v>
+        <v>365</v>
       </c>
       <c r="D102">
         <f t="shared" si="1"/>
-        <v>-21891</v>
+        <v>8759</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A103" s="2">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B103" t="s">
         <v>4</v>
       </c>
       <c r="C103">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="D103">
         <f t="shared" si="1"/>
-        <v>-22100</v>
+        <v>8599</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A104" s="2">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B104" t="s">
         <v>4</v>
       </c>
       <c r="C104">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="D104">
         <f t="shared" si="1"/>
-        <v>-22400</v>
+        <v>8259</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A105" s="2">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B105" t="s">
         <v>4</v>
       </c>
       <c r="C105">
-        <v>2100</v>
+        <v>150</v>
       </c>
       <c r="D105">
         <f t="shared" si="1"/>
-        <v>-24500</v>
+        <v>8109</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A106" s="2">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B106" t="s">
         <v>4</v>
       </c>
       <c r="C106">
-        <v>2050</v>
+        <v>209</v>
       </c>
       <c r="D106">
         <f t="shared" si="1"/>
-        <v>-26550</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A107" s="2">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B107" t="s">
         <v>4</v>
       </c>
       <c r="C107">
-        <v>173</v>
+        <v>300</v>
       </c>
       <c r="D107">
         <f t="shared" si="1"/>
-        <v>-26723</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.45">
@@ -2062,656 +2066,656 @@
         <v>4</v>
       </c>
       <c r="C108">
-        <v>120</v>
+        <v>2100</v>
       </c>
       <c r="D108">
         <f t="shared" si="1"/>
-        <v>-26843</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" s="2">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B109" t="s">
         <v>4</v>
       </c>
-      <c r="C109" s="1">
-        <v>105</v>
+      <c r="C109">
+        <v>2050</v>
       </c>
       <c r="D109">
         <f t="shared" si="1"/>
-        <v>-26948</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A110" s="2">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B110" t="s">
         <v>4</v>
       </c>
       <c r="C110">
-        <v>76</v>
+        <v>173</v>
       </c>
       <c r="D110">
         <f t="shared" si="1"/>
-        <v>-27024</v>
+        <v>3277</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A111" s="2">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B111" t="s">
         <v>4</v>
       </c>
       <c r="C111">
-        <v>350</v>
+        <v>120</v>
       </c>
       <c r="D111">
         <f t="shared" si="1"/>
-        <v>-27374</v>
+        <v>3157</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A112" s="2">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B112" t="s">
         <v>4</v>
       </c>
-      <c r="C112">
-        <v>70</v>
+      <c r="C112" s="1">
+        <v>105</v>
       </c>
       <c r="D112">
         <f t="shared" si="1"/>
-        <v>-27444</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A113" s="2">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B113" t="s">
         <v>4</v>
       </c>
       <c r="C113">
-        <v>180</v>
+        <v>76</v>
       </c>
       <c r="D113">
         <f t="shared" si="1"/>
-        <v>-27624</v>
+        <v>2976</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A114" s="2">
-        <v>45938</v>
+        <v>45943</v>
       </c>
       <c r="B114" t="s">
         <v>4</v>
       </c>
       <c r="C114">
-        <v>508</v>
+        <v>350</v>
       </c>
       <c r="D114">
         <f t="shared" si="1"/>
-        <v>-28132</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A115" s="2">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B115" t="s">
         <v>4</v>
       </c>
       <c r="C115">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="D115">
         <f t="shared" si="1"/>
-        <v>-28262</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A116" s="2">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B116" t="s">
         <v>4</v>
       </c>
       <c r="C116">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="D116">
         <f t="shared" si="1"/>
-        <v>-28352</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A117" s="2">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B117" t="s">
         <v>4</v>
       </c>
       <c r="C117">
-        <v>45</v>
+        <v>508</v>
       </c>
       <c r="D117">
         <f t="shared" si="1"/>
-        <v>-28397</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A118" s="2">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B118" t="s">
         <v>4</v>
       </c>
       <c r="C118">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="D118">
         <f t="shared" si="1"/>
-        <v>-28597</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A119" s="2">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B119" t="s">
         <v>4</v>
       </c>
       <c r="C119">
-        <v>835</v>
+        <v>90</v>
       </c>
       <c r="D119">
         <f t="shared" si="1"/>
-        <v>-29432</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A120" s="2">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B120" t="s">
         <v>4</v>
       </c>
       <c r="C120">
-        <v>1500</v>
+        <v>45</v>
       </c>
       <c r="D120">
         <f t="shared" si="1"/>
-        <v>-30932</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A121" s="2">
-        <v>45932</v>
+        <v>45937</v>
       </c>
       <c r="B121" t="s">
         <v>4</v>
       </c>
       <c r="C121">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="D121">
         <f t="shared" si="1"/>
-        <v>-31062</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A122" s="2">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B122" t="s">
         <v>4</v>
       </c>
       <c r="C122">
-        <v>248</v>
+        <v>835</v>
       </c>
       <c r="D122">
         <f t="shared" si="1"/>
-        <v>-31310</v>
+        <v>568</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A123" s="2">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B123" t="s">
         <v>4</v>
       </c>
       <c r="C123">
-        <v>85</v>
+        <v>1500</v>
       </c>
       <c r="D123">
         <f t="shared" si="1"/>
-        <v>-31395</v>
+        <v>-932</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A124" s="2">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B124" t="s">
         <v>4</v>
       </c>
       <c r="C124">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D124">
         <f t="shared" si="1"/>
-        <v>-31514</v>
+        <v>-1062</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A125" s="2">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B125" t="s">
         <v>4</v>
       </c>
       <c r="C125">
-        <v>165</v>
+        <v>248</v>
       </c>
       <c r="D125">
         <f t="shared" si="1"/>
-        <v>-31679</v>
+        <v>-1310</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A126" s="2">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B126" t="s">
         <v>4</v>
       </c>
       <c r="C126">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D126">
         <f t="shared" si="1"/>
-        <v>-31780</v>
+        <v>-1395</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A127" s="2">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B127" t="s">
         <v>4</v>
       </c>
       <c r="C127">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="D127">
         <f t="shared" si="1"/>
-        <v>-31939</v>
+        <v>-1514</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A128" s="2">
-        <v>45926</v>
+        <v>45931</v>
       </c>
       <c r="B128" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C128">
-        <v>145</v>
+        <v>10000</v>
       </c>
       <c r="D128">
         <f t="shared" si="1"/>
-        <v>-32084</v>
+        <v>8486</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A129" s="2">
-        <v>45925</v>
+        <v>45930</v>
       </c>
       <c r="B129" t="s">
         <v>4</v>
       </c>
       <c r="C129">
-        <v>45</v>
+        <v>165</v>
       </c>
       <c r="D129">
         <f t="shared" si="1"/>
-        <v>-32129</v>
+        <v>8321</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A130" s="2">
-        <v>45925</v>
+        <v>45930</v>
       </c>
       <c r="B130" t="s">
         <v>4</v>
       </c>
       <c r="C130">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="D130">
         <f t="shared" si="1"/>
-        <v>-32164</v>
+        <v>8220</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A131" s="2">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B131" t="s">
         <v>4</v>
       </c>
       <c r="C131">
-        <v>310</v>
+        <v>159</v>
       </c>
       <c r="D131">
         <f t="shared" ref="D131:D194" si="2">IF(B131="Income",D130+C131,D130-C131)</f>
-        <v>-32474</v>
+        <v>8061</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A132" s="2">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B132" t="s">
         <v>4</v>
       </c>
       <c r="C132">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="D132">
         <f t="shared" si="2"/>
-        <v>-32579</v>
+        <v>7916</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A133" s="2">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B133" t="s">
         <v>4</v>
       </c>
       <c r="C133">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="D133">
         <f t="shared" si="2"/>
-        <v>-32678</v>
+        <v>7871</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A134" s="2">
-        <v>45922</v>
+        <v>45925</v>
       </c>
       <c r="B134" t="s">
         <v>4</v>
       </c>
       <c r="C134">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="D134">
         <f t="shared" si="2"/>
-        <v>-32758</v>
+        <v>7836</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A135" s="2">
-        <v>45922</v>
+        <v>45925</v>
       </c>
       <c r="B135" t="s">
         <v>4</v>
       </c>
       <c r="C135">
-        <v>125</v>
+        <v>310</v>
       </c>
       <c r="D135">
         <f t="shared" si="2"/>
-        <v>-32883</v>
+        <v>7526</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A136" s="2">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B136" t="s">
         <v>4</v>
       </c>
       <c r="C136">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="D136">
         <f t="shared" si="2"/>
-        <v>-33008</v>
+        <v>7421</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A137" s="2">
-        <v>45921</v>
+        <v>45923</v>
       </c>
       <c r="B137" t="s">
         <v>4</v>
       </c>
       <c r="C137">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D137">
         <f t="shared" si="2"/>
-        <v>-33113</v>
+        <v>7322</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A138" s="2">
-        <v>45921</v>
+        <v>45922</v>
       </c>
       <c r="B138" t="s">
         <v>4</v>
       </c>
       <c r="C138">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D138">
         <f t="shared" si="2"/>
-        <v>-33202</v>
+        <v>7242</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A139" s="2">
-        <v>45920</v>
+        <v>45922</v>
       </c>
       <c r="B139" t="s">
         <v>4</v>
       </c>
       <c r="C139">
-        <v>185</v>
+        <v>125</v>
       </c>
       <c r="D139">
         <f t="shared" si="2"/>
-        <v>-33387</v>
+        <v>7117</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A140" s="2">
-        <v>45920</v>
+        <v>45922</v>
       </c>
       <c r="B140" t="s">
         <v>4</v>
       </c>
       <c r="C140">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="D140">
         <f t="shared" si="2"/>
-        <v>-33442</v>
+        <v>6992</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A141" s="2">
-        <v>45920</v>
+        <v>45921</v>
       </c>
       <c r="B141" t="s">
         <v>4</v>
       </c>
       <c r="C141">
-        <v>280</v>
+        <v>105</v>
       </c>
       <c r="D141">
         <f t="shared" si="2"/>
-        <v>-33722</v>
+        <v>6887</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A142" s="2">
-        <v>45919</v>
+        <v>45921</v>
       </c>
       <c r="B142" t="s">
         <v>4</v>
       </c>
       <c r="C142">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="D142">
         <f t="shared" si="2"/>
-        <v>-33842</v>
+        <v>6798</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A143" s="2">
-        <v>45919</v>
+        <v>45920</v>
       </c>
       <c r="B143" t="s">
         <v>4</v>
       </c>
       <c r="C143">
-        <v>60</v>
+        <v>185</v>
       </c>
       <c r="D143">
         <f t="shared" si="2"/>
-        <v>-33902</v>
+        <v>6613</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A144" s="2">
-        <v>45919</v>
+        <v>45920</v>
       </c>
       <c r="B144" t="s">
         <v>4</v>
       </c>
       <c r="C144">
-        <v>294</v>
+        <v>55</v>
       </c>
       <c r="D144">
         <f t="shared" si="2"/>
-        <v>-34196</v>
+        <v>6558</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" s="2">
-        <v>45918</v>
+        <v>45920</v>
       </c>
       <c r="B145" t="s">
         <v>4</v>
       </c>
       <c r="C145">
-        <v>124</v>
+        <v>280</v>
       </c>
       <c r="D145">
         <f t="shared" si="2"/>
-        <v>-34320</v>
+        <v>6278</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A146" s="2">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B146" t="s">
         <v>4</v>
       </c>
       <c r="C146">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D146">
         <f t="shared" si="2"/>
-        <v>-34432</v>
+        <v>6158</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A147" s="2">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B147" t="s">
         <v>4</v>
       </c>
       <c r="C147">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="D147">
         <f t="shared" si="2"/>
-        <v>-34567</v>
+        <v>6098</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A148" s="2">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B148" t="s">
         <v>4</v>
       </c>
       <c r="C148">
-        <v>160</v>
+        <v>294</v>
       </c>
       <c r="D148">
         <f t="shared" si="2"/>
-        <v>-34727</v>
+        <v>5804</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A149" s="2">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B149" t="s">
         <v>4</v>
       </c>
       <c r="C149">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="D149">
         <f t="shared" si="2"/>
-        <v>-34822</v>
+        <v>5680</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A150" s="2">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B150" t="s">
         <v>4</v>
       </c>
       <c r="C150">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="D150">
         <f t="shared" si="2"/>
-        <v>-34876</v>
+        <v>5568</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A151" s="2">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B151" t="s">
         <v>4</v>
       </c>
       <c r="C151">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="D151">
         <f t="shared" si="2"/>
-        <v>-34931</v>
+        <v>5433</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.45">
@@ -2722,176 +2726,176 @@
         <v>4</v>
       </c>
       <c r="C152">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="D152">
         <f t="shared" si="2"/>
-        <v>-34991</v>
+        <v>5273</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A153" s="2">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B153" t="s">
         <v>4</v>
       </c>
       <c r="C153">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="D153">
         <f t="shared" si="2"/>
-        <v>-35036</v>
+        <v>5178</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A154" s="2">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B154" t="s">
         <v>4</v>
       </c>
       <c r="C154">
-        <v>210</v>
+        <v>54</v>
       </c>
       <c r="D154">
         <f t="shared" si="2"/>
-        <v>-35246</v>
+        <v>5124</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A155" s="2">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B155" t="s">
         <v>4</v>
       </c>
       <c r="C155">
-        <v>170</v>
+        <v>55</v>
       </c>
       <c r="D155">
         <f t="shared" si="2"/>
-        <v>-35416</v>
+        <v>5069</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A156" s="2">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B156" t="s">
         <v>4</v>
       </c>
       <c r="C156">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D156">
         <f t="shared" si="2"/>
-        <v>-35466</v>
+        <v>5009</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A157" s="2">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B157" t="s">
         <v>4</v>
       </c>
       <c r="C157">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D157">
         <f t="shared" si="2"/>
-        <v>-35536</v>
+        <v>4964</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A158" s="2">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B158" t="s">
         <v>4</v>
       </c>
       <c r="C158">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="D158">
         <f t="shared" si="2"/>
-        <v>-35561</v>
+        <v>4754</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A159" s="2">
-        <v>45827</v>
+        <v>45916</v>
       </c>
       <c r="B159" t="s">
         <v>4</v>
       </c>
       <c r="C159">
-        <v>758</v>
+        <v>170</v>
       </c>
       <c r="D159">
         <f t="shared" si="2"/>
-        <v>-36319</v>
+        <v>4584</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A160" s="2">
-        <v>45827</v>
+        <v>45916</v>
       </c>
       <c r="B160" t="s">
         <v>4</v>
       </c>
       <c r="C160">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D160">
         <f t="shared" si="2"/>
-        <v>-36519</v>
+        <v>4534</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A161" s="2">
-        <v>45827</v>
+        <v>45915</v>
       </c>
       <c r="B161" t="s">
         <v>4</v>
       </c>
       <c r="C161">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="D161">
         <f t="shared" si="2"/>
-        <v>-36629</v>
+        <v>4464</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A162" s="2">
-        <v>45827</v>
+        <v>45915</v>
       </c>
       <c r="B162" t="s">
         <v>4</v>
       </c>
       <c r="C162">
-        <v>360</v>
+        <v>25</v>
       </c>
       <c r="D162">
         <f t="shared" si="2"/>
-        <v>-36989</v>
+        <v>4439</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A163" s="2">
-        <v>45827</v>
+        <v>45901</v>
       </c>
       <c r="B163" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C163">
-        <v>242</v>
+        <v>10000</v>
       </c>
       <c r="D163">
         <f t="shared" si="2"/>
-        <v>-37231</v>
+        <v>14439</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.45">
@@ -2902,286 +2906,286 @@
         <v>4</v>
       </c>
       <c r="C164">
-        <v>85</v>
+        <v>758</v>
       </c>
       <c r="D164">
         <f t="shared" si="2"/>
-        <v>-37316</v>
+        <v>13681</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A165" s="2">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="B165" t="s">
         <v>4</v>
       </c>
       <c r="C165">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="D165">
         <f t="shared" si="2"/>
-        <v>-37481</v>
+        <v>13481</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A166" s="2">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="B166" t="s">
         <v>4</v>
       </c>
       <c r="C166">
-        <v>378</v>
+        <v>110</v>
       </c>
       <c r="D166">
         <f t="shared" si="2"/>
-        <v>-37859</v>
+        <v>13371</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A167" s="2">
-        <v>45825</v>
+        <v>45827</v>
       </c>
       <c r="B167" t="s">
         <v>4</v>
       </c>
       <c r="C167">
-        <v>110</v>
+        <v>360</v>
       </c>
       <c r="D167">
         <f t="shared" si="2"/>
-        <v>-37969</v>
+        <v>13011</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A168" s="2">
-        <v>45823</v>
+        <v>45827</v>
       </c>
       <c r="B168" t="s">
         <v>4</v>
       </c>
       <c r="C168">
-        <v>179</v>
+        <v>242</v>
       </c>
       <c r="D168">
         <f t="shared" si="2"/>
-        <v>-38148</v>
+        <v>12769</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A169" s="2">
-        <v>45823</v>
+        <v>45827</v>
       </c>
       <c r="B169" t="s">
         <v>4</v>
       </c>
       <c r="C169">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="D169">
         <f t="shared" si="2"/>
-        <v>-38253</v>
+        <v>12684</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A170" s="2">
-        <v>45823</v>
+        <v>45826</v>
       </c>
       <c r="B170" t="s">
         <v>4</v>
       </c>
       <c r="C170">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="D170">
         <f t="shared" si="2"/>
-        <v>-38303</v>
+        <v>12519</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A171" s="2">
-        <v>45823</v>
+        <v>45826</v>
       </c>
       <c r="B171" t="s">
         <v>4</v>
       </c>
       <c r="C171">
-        <v>25</v>
+        <v>378</v>
       </c>
       <c r="D171">
         <f t="shared" si="2"/>
-        <v>-38328</v>
+        <v>12141</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A172" s="2">
-        <v>45823</v>
+        <v>45825</v>
       </c>
       <c r="B172" t="s">
         <v>4</v>
       </c>
       <c r="C172">
-        <v>209</v>
+        <v>110</v>
       </c>
       <c r="D172">
         <f t="shared" si="2"/>
-        <v>-38537</v>
+        <v>12031</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A173" s="2">
-        <v>45822</v>
+        <v>45823</v>
       </c>
       <c r="B173" t="s">
         <v>4</v>
       </c>
       <c r="C173">
-        <v>50</v>
+        <v>179</v>
       </c>
       <c r="D173">
         <f t="shared" si="2"/>
-        <v>-38587</v>
+        <v>11852</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A174" s="2">
-        <v>45822</v>
+        <v>45823</v>
       </c>
       <c r="B174" t="s">
         <v>4</v>
       </c>
       <c r="C174">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="D174">
         <f t="shared" si="2"/>
-        <v>-38717</v>
+        <v>11747</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A175" s="2">
-        <v>45822</v>
+        <v>45823</v>
       </c>
       <c r="B175" t="s">
         <v>4</v>
       </c>
       <c r="C175">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="D175">
         <f t="shared" si="2"/>
-        <v>-38822</v>
+        <v>11697</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A176" s="2">
-        <v>45821</v>
+        <v>45823</v>
       </c>
       <c r="B176" t="s">
         <v>4</v>
       </c>
       <c r="C176">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D176">
         <f t="shared" si="2"/>
-        <v>-38852</v>
+        <v>11672</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A177" s="2">
-        <v>45821</v>
+        <v>45823</v>
       </c>
       <c r="B177" t="s">
         <v>4</v>
       </c>
       <c r="C177">
-        <v>255</v>
+        <v>209</v>
       </c>
       <c r="D177">
         <f t="shared" si="2"/>
-        <v>-39107</v>
+        <v>11463</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A178" s="2">
-        <v>45820</v>
+        <v>45822</v>
       </c>
       <c r="B178" t="s">
         <v>4</v>
       </c>
       <c r="C178">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D178">
         <f t="shared" si="2"/>
-        <v>-39207</v>
+        <v>11413</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A179" s="2">
-        <v>45820</v>
+        <v>45822</v>
       </c>
       <c r="B179" t="s">
         <v>4</v>
       </c>
       <c r="C179">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="D179">
         <f t="shared" si="2"/>
-        <v>-39407</v>
+        <v>11283</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A180" s="2">
-        <v>45819</v>
+        <v>45822</v>
       </c>
       <c r="B180" t="s">
         <v>4</v>
       </c>
       <c r="C180">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="D180">
         <f t="shared" si="2"/>
-        <v>-39442</v>
+        <v>11178</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A181" s="2">
-        <v>45819</v>
+        <v>45821</v>
       </c>
       <c r="B181" t="s">
         <v>4</v>
       </c>
       <c r="C181">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="D181">
         <f t="shared" si="2"/>
-        <v>-39526</v>
+        <v>11148</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A182" s="2">
-        <v>45819</v>
+        <v>45821</v>
       </c>
       <c r="B182" t="s">
         <v>4</v>
       </c>
       <c r="C182">
-        <v>60</v>
+        <v>255</v>
       </c>
       <c r="D182">
         <f t="shared" si="2"/>
-        <v>-39586</v>
+        <v>10893</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A183" s="2">
-        <v>45819</v>
+        <v>45820</v>
       </c>
       <c r="B183" t="s">
         <v>4</v>
@@ -3191,1332 +3195,1332 @@
       </c>
       <c r="D183">
         <f t="shared" si="2"/>
-        <v>-39686</v>
+        <v>10793</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A184" s="2">
-        <v>45818</v>
+        <v>45820</v>
       </c>
       <c r="B184" t="s">
         <v>4</v>
       </c>
       <c r="C184">
-        <v>89</v>
+        <v>200</v>
       </c>
       <c r="D184">
         <f t="shared" si="2"/>
-        <v>-39775</v>
+        <v>10593</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A185" s="2">
-        <v>45818</v>
+        <v>45819</v>
       </c>
       <c r="B185" t="s">
         <v>4</v>
       </c>
       <c r="C185">
-        <v>180</v>
+        <v>35</v>
       </c>
       <c r="D185">
         <f t="shared" si="2"/>
-        <v>-39955</v>
+        <v>10558</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A186" s="2">
-        <v>45818</v>
+        <v>45819</v>
       </c>
       <c r="B186" t="s">
         <v>4</v>
       </c>
       <c r="C186">
-        <v>250</v>
+        <v>84</v>
       </c>
       <c r="D186">
         <f t="shared" si="2"/>
-        <v>-40205</v>
+        <v>10474</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A187" s="2">
-        <v>45818</v>
+        <v>45819</v>
       </c>
       <c r="B187" t="s">
         <v>4</v>
       </c>
       <c r="C187">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D187">
         <f t="shared" si="2"/>
-        <v>-40270</v>
+        <v>10414</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A188" s="2">
-        <v>45813</v>
+        <v>45819</v>
       </c>
       <c r="B188" t="s">
         <v>4</v>
       </c>
       <c r="C188">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="D188">
         <f t="shared" si="2"/>
-        <v>-40430</v>
+        <v>10314</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A189" s="2">
-        <v>45812</v>
+        <v>45818</v>
       </c>
       <c r="B189" t="s">
         <v>4</v>
       </c>
       <c r="C189">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="D189">
         <f t="shared" si="2"/>
-        <v>-40560</v>
+        <v>10225</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A190" s="2">
-        <v>45812</v>
+        <v>45818</v>
       </c>
       <c r="B190" t="s">
         <v>4</v>
       </c>
       <c r="C190">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="D190">
         <f t="shared" si="2"/>
-        <v>-40690</v>
+        <v>10045</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A191" s="2">
-        <v>45812</v>
+        <v>45818</v>
       </c>
       <c r="B191" t="s">
         <v>4</v>
       </c>
       <c r="C191">
-        <v>79</v>
+        <v>250</v>
       </c>
       <c r="D191">
         <f t="shared" si="2"/>
-        <v>-40769</v>
+        <v>9795</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A192" s="2">
-        <v>45811</v>
+        <v>45818</v>
       </c>
       <c r="B192" t="s">
         <v>4</v>
       </c>
       <c r="C192">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="D192">
         <f t="shared" si="2"/>
-        <v>-40904</v>
+        <v>9730</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A193" s="2">
-        <v>45811</v>
+        <v>45813</v>
       </c>
       <c r="B193" t="s">
         <v>4</v>
       </c>
       <c r="C193">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="D193">
         <f t="shared" si="2"/>
-        <v>-40969</v>
+        <v>9570</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A194" s="2">
-        <v>45811</v>
+        <v>45812</v>
       </c>
       <c r="B194" t="s">
         <v>4</v>
       </c>
       <c r="C194">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="D194">
         <f t="shared" si="2"/>
-        <v>-41067</v>
+        <v>9440</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A195" s="2">
-        <v>45810</v>
+        <v>45812</v>
       </c>
       <c r="B195" t="s">
         <v>4</v>
       </c>
       <c r="C195">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="D195">
         <f t="shared" ref="D195:D258" si="3">IF(B195="Income",D194+C195,D194-C195)</f>
-        <v>-41167</v>
+        <v>9310</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A196" s="2">
-        <v>45810</v>
+        <v>45812</v>
       </c>
       <c r="B196" t="s">
         <v>4</v>
       </c>
       <c r="C196">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="D196">
         <f t="shared" si="3"/>
-        <v>-41272</v>
+        <v>9231</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A197" s="2">
-        <v>45810</v>
+        <v>45811</v>
       </c>
       <c r="B197" t="s">
         <v>4</v>
       </c>
       <c r="C197">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="D197">
         <f t="shared" si="3"/>
-        <v>-41362</v>
+        <v>9096</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A198" s="2">
-        <v>45810</v>
+        <v>45811</v>
       </c>
       <c r="B198" t="s">
         <v>4</v>
       </c>
       <c r="C198">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="D198">
         <f t="shared" si="3"/>
-        <v>-41417</v>
+        <v>9031</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A199" s="2">
-        <v>45809</v>
+        <v>45811</v>
       </c>
       <c r="B199" t="s">
         <v>4</v>
       </c>
       <c r="C199">
-        <v>177</v>
+        <v>98</v>
       </c>
       <c r="D199">
         <f t="shared" si="3"/>
-        <v>-41594</v>
+        <v>8933</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A200" s="2">
-        <v>45809</v>
+        <v>45810</v>
       </c>
       <c r="B200" t="s">
         <v>4</v>
       </c>
       <c r="C200">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D200">
         <f t="shared" si="3"/>
-        <v>-41714</v>
+        <v>8833</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A201" s="2">
-        <v>45806</v>
+        <v>45810</v>
       </c>
       <c r="B201" t="s">
         <v>4</v>
       </c>
       <c r="C201">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="D201">
         <f t="shared" si="3"/>
-        <v>-41793</v>
+        <v>8728</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A202" s="2">
-        <v>45806</v>
+        <v>45810</v>
       </c>
       <c r="B202" t="s">
         <v>4</v>
       </c>
       <c r="C202">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D202">
         <f t="shared" si="3"/>
-        <v>-41897</v>
+        <v>8638</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A203" s="2">
-        <v>45806</v>
+        <v>45810</v>
       </c>
       <c r="B203" t="s">
         <v>4</v>
       </c>
       <c r="C203">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="D203">
         <f t="shared" si="3"/>
-        <v>-42017</v>
+        <v>8583</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A204" s="2">
-        <v>45805</v>
+        <v>45809</v>
       </c>
       <c r="B204" t="s">
         <v>4</v>
       </c>
       <c r="C204">
-        <v>108</v>
+        <v>177</v>
       </c>
       <c r="D204">
         <f t="shared" si="3"/>
-        <v>-42125</v>
+        <v>8406</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A205" s="2">
-        <v>45805</v>
+        <v>45809</v>
       </c>
       <c r="B205" t="s">
         <v>4</v>
       </c>
       <c r="C205">
-        <v>265</v>
+        <v>120</v>
       </c>
       <c r="D205">
         <f t="shared" si="3"/>
-        <v>-42390</v>
+        <v>8286</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A206" s="2">
-        <v>45805</v>
+        <v>45809</v>
       </c>
       <c r="B206" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C206">
-        <v>168</v>
+        <v>10000</v>
       </c>
       <c r="D206">
         <f t="shared" si="3"/>
-        <v>-42558</v>
+        <v>18286</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A207" s="2">
-        <v>45804</v>
+        <v>45806</v>
       </c>
       <c r="B207" t="s">
         <v>4</v>
       </c>
       <c r="C207">
-        <v>260</v>
+        <v>79</v>
       </c>
       <c r="D207">
         <f t="shared" si="3"/>
-        <v>-42818</v>
+        <v>18207</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A208" s="2">
-        <v>45804</v>
+        <v>45806</v>
       </c>
       <c r="B208" t="s">
         <v>4</v>
       </c>
       <c r="C208">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="D208">
         <f t="shared" si="3"/>
-        <v>-42942</v>
+        <v>18103</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A209" s="2">
-        <v>45802</v>
+        <v>45806</v>
       </c>
       <c r="B209" t="s">
         <v>4</v>
       </c>
       <c r="C209">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="D209">
         <f t="shared" si="3"/>
-        <v>-43530</v>
+        <v>17983</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A210" s="2">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="B210" t="s">
         <v>4</v>
       </c>
       <c r="C210">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D210">
         <f t="shared" si="3"/>
-        <v>-43635</v>
+        <v>17875</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A211" s="2">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="B211" t="s">
         <v>4</v>
       </c>
       <c r="C211">
-        <v>70</v>
+        <v>265</v>
       </c>
       <c r="D211">
         <f t="shared" si="3"/>
-        <v>-43705</v>
+        <v>17610</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A212" s="2">
-        <v>45799</v>
+        <v>45805</v>
       </c>
       <c r="B212" t="s">
         <v>4</v>
       </c>
       <c r="C212">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="D212">
         <f t="shared" si="3"/>
-        <v>-43824</v>
+        <v>17442</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A213" s="2">
-        <v>45799</v>
+        <v>45804</v>
       </c>
       <c r="B213" t="s">
         <v>4</v>
       </c>
       <c r="C213">
-        <v>70</v>
+        <v>260</v>
       </c>
       <c r="D213">
         <f t="shared" si="3"/>
-        <v>-43894</v>
+        <v>17182</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A214" s="2">
-        <v>45798</v>
+        <v>45804</v>
       </c>
       <c r="B214" t="s">
         <v>4</v>
       </c>
       <c r="C214">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="D214">
         <f t="shared" si="3"/>
-        <v>-43944</v>
+        <v>17058</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A215" s="2">
-        <v>45798</v>
+        <v>45802</v>
       </c>
       <c r="B215" t="s">
         <v>4</v>
       </c>
       <c r="C215">
-        <v>98</v>
+        <v>588</v>
       </c>
       <c r="D215">
         <f t="shared" si="3"/>
-        <v>-44042</v>
+        <v>16470</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A216" s="2">
-        <v>45797</v>
+        <v>45800</v>
       </c>
       <c r="B216" t="s">
         <v>4</v>
       </c>
       <c r="C216">
-        <v>600</v>
+        <v>105</v>
       </c>
       <c r="D216">
         <f t="shared" si="3"/>
-        <v>-44642</v>
+        <v>16365</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A217" s="2">
-        <v>45797</v>
+        <v>45800</v>
       </c>
       <c r="B217" t="s">
         <v>4</v>
       </c>
       <c r="C217">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="D217">
         <f t="shared" si="3"/>
-        <v>-44669</v>
+        <v>16295</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A218" s="2">
-        <v>45792</v>
+        <v>45799</v>
       </c>
       <c r="B218" t="s">
         <v>4</v>
       </c>
       <c r="C218">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="D218">
         <f t="shared" si="3"/>
-        <v>-44739</v>
+        <v>16176</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A219" s="2">
-        <v>45791</v>
+        <v>45799</v>
       </c>
       <c r="B219" t="s">
         <v>4</v>
       </c>
       <c r="C219">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D219">
         <f t="shared" si="3"/>
-        <v>-44829</v>
+        <v>16106</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A220" s="2">
-        <v>45791</v>
+        <v>45798</v>
       </c>
       <c r="B220" t="s">
         <v>4</v>
       </c>
       <c r="C220">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D220">
         <f t="shared" si="3"/>
-        <v>-44913</v>
+        <v>16056</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A221" s="2">
-        <v>45790</v>
+        <v>45798</v>
       </c>
       <c r="B221" t="s">
         <v>4</v>
       </c>
       <c r="C221">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="D221">
         <f t="shared" si="3"/>
-        <v>-44978</v>
+        <v>15958</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A222" s="2">
-        <v>45790</v>
+        <v>45797</v>
       </c>
       <c r="B222" t="s">
         <v>4</v>
       </c>
       <c r="C222">
-        <v>48</v>
+        <v>600</v>
       </c>
       <c r="D222">
         <f t="shared" si="3"/>
-        <v>-45026</v>
+        <v>15358</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A223" s="2">
-        <v>45790</v>
+        <v>45797</v>
       </c>
       <c r="B223" t="s">
         <v>4</v>
       </c>
       <c r="C223">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="D223">
         <f t="shared" si="3"/>
-        <v>-45136</v>
+        <v>15331</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A224" s="2">
-        <v>45790</v>
+        <v>45792</v>
       </c>
       <c r="B224" t="s">
         <v>4</v>
       </c>
       <c r="C224">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D224">
         <f t="shared" si="3"/>
-        <v>-45191</v>
+        <v>15261</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A225" s="2">
-        <v>45789</v>
+        <v>45791</v>
       </c>
       <c r="B225" t="s">
         <v>4</v>
       </c>
       <c r="C225">
-        <v>184</v>
+        <v>90</v>
       </c>
       <c r="D225">
         <f t="shared" si="3"/>
-        <v>-45375</v>
+        <v>15171</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A226" s="2">
-        <v>45789</v>
+        <v>45791</v>
       </c>
       <c r="B226" t="s">
         <v>4</v>
       </c>
       <c r="C226">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D226">
         <f t="shared" si="3"/>
-        <v>-45463</v>
+        <v>15087</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A227" s="2">
-        <v>45788</v>
+        <v>45790</v>
       </c>
       <c r="B227" t="s">
         <v>4</v>
       </c>
       <c r="C227">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D227">
         <f t="shared" si="3"/>
-        <v>-45512</v>
+        <v>15022</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A228" s="2">
-        <v>45787</v>
+        <v>45790</v>
       </c>
       <c r="B228" t="s">
         <v>4</v>
       </c>
       <c r="C228">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D228">
         <f t="shared" si="3"/>
-        <v>-45551</v>
+        <v>14974</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A229" s="2">
-        <v>45786</v>
+        <v>45790</v>
       </c>
       <c r="B229" t="s">
         <v>4</v>
       </c>
       <c r="C229">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D229">
         <f t="shared" si="3"/>
-        <v>-45676</v>
+        <v>14864</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A230" s="2">
-        <v>45786</v>
+        <v>45790</v>
       </c>
       <c r="B230" t="s">
         <v>4</v>
       </c>
       <c r="C230">
-        <v>147</v>
+        <v>55</v>
       </c>
       <c r="D230">
         <f t="shared" si="3"/>
-        <v>-45823</v>
+        <v>14809</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A231" s="2">
-        <v>45785</v>
+        <v>45789</v>
       </c>
       <c r="B231" t="s">
         <v>4</v>
       </c>
       <c r="C231">
-        <v>125</v>
+        <v>184</v>
       </c>
       <c r="D231">
         <f t="shared" si="3"/>
-        <v>-45948</v>
+        <v>14625</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A232" s="2">
-        <v>45784</v>
+        <v>45789</v>
       </c>
       <c r="B232" t="s">
         <v>4</v>
       </c>
       <c r="C232">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D232">
         <f t="shared" si="3"/>
-        <v>-46050</v>
+        <v>14537</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A233" s="2">
-        <v>45784</v>
+        <v>45788</v>
       </c>
       <c r="B233" t="s">
         <v>4</v>
       </c>
       <c r="C233">
-        <v>628</v>
+        <v>49</v>
       </c>
       <c r="D233">
         <f t="shared" si="3"/>
-        <v>-46678</v>
+        <v>14488</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A234" s="2">
-        <v>45784</v>
+        <v>45787</v>
       </c>
       <c r="B234" t="s">
         <v>4</v>
       </c>
       <c r="C234">
-        <v>180</v>
+        <v>39</v>
       </c>
       <c r="D234">
         <f t="shared" si="3"/>
-        <v>-46858</v>
+        <v>14449</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A235" s="2">
-        <v>45783</v>
+        <v>45786</v>
       </c>
       <c r="B235" t="s">
         <v>4</v>
       </c>
       <c r="C235">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D235">
         <f t="shared" si="3"/>
-        <v>-46967</v>
+        <v>14324</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A236" s="2">
-        <v>45783</v>
+        <v>45786</v>
       </c>
       <c r="B236" t="s">
         <v>4</v>
       </c>
       <c r="C236">
-        <v>48</v>
+        <v>147</v>
       </c>
       <c r="D236">
         <f t="shared" si="3"/>
-        <v>-47015</v>
+        <v>14177</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A237" s="2">
-        <v>45783</v>
+        <v>45785</v>
       </c>
       <c r="B237" t="s">
         <v>4</v>
       </c>
       <c r="C237">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="D237">
         <f t="shared" si="3"/>
-        <v>-47125</v>
+        <v>14052</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A238" s="2">
-        <v>45782</v>
+        <v>45784</v>
       </c>
       <c r="B238" t="s">
         <v>4</v>
       </c>
-      <c r="C238" s="1">
-        <v>50</v>
+      <c r="C238">
+        <v>102</v>
       </c>
       <c r="D238">
         <f t="shared" si="3"/>
-        <v>-47175</v>
+        <v>13950</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A239" s="2">
-        <v>45780</v>
+        <v>45784</v>
       </c>
       <c r="B239" t="s">
         <v>4</v>
       </c>
       <c r="C239">
-        <v>5525</v>
+        <v>628</v>
       </c>
       <c r="D239">
         <f t="shared" si="3"/>
-        <v>-52700</v>
+        <v>13322</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A240" s="2">
-        <v>45780</v>
+        <v>45784</v>
       </c>
       <c r="B240" t="s">
         <v>4</v>
       </c>
       <c r="C240">
-        <v>289</v>
+        <v>180</v>
       </c>
       <c r="D240">
         <f t="shared" si="3"/>
-        <v>-52989</v>
+        <v>13142</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A241" s="2">
-        <v>45779</v>
+        <v>45783</v>
       </c>
       <c r="B241" t="s">
         <v>4</v>
       </c>
       <c r="C241">
-        <v>200</v>
+        <v>109</v>
       </c>
       <c r="D241">
         <f t="shared" si="3"/>
-        <v>-53189</v>
+        <v>13033</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A242" s="2">
-        <v>45779</v>
+        <v>45783</v>
       </c>
       <c r="B242" t="s">
         <v>4</v>
       </c>
       <c r="C242">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="D242">
         <f t="shared" si="3"/>
-        <v>-53389</v>
+        <v>12985</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A243" s="2">
-        <v>45779</v>
+        <v>45783</v>
       </c>
       <c r="B243" t="s">
         <v>4</v>
       </c>
       <c r="C243">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D243">
         <f t="shared" si="3"/>
-        <v>-53491</v>
+        <v>12875</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A244" s="2">
-        <v>45778</v>
+        <v>45782</v>
       </c>
       <c r="B244" t="s">
         <v>4</v>
       </c>
-      <c r="C244">
-        <v>117</v>
+      <c r="C244" s="1">
+        <v>50</v>
       </c>
       <c r="D244">
         <f t="shared" si="3"/>
-        <v>-53608</v>
+        <v>12825</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A245" s="2">
-        <v>45778</v>
+        <v>45780</v>
       </c>
       <c r="B245" t="s">
         <v>4</v>
       </c>
       <c r="C245">
-        <v>60</v>
+        <v>5525</v>
       </c>
       <c r="D245">
         <f t="shared" si="3"/>
-        <v>-53668</v>
+        <v>7300</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A246" s="2">
-        <v>45778</v>
+        <v>45780</v>
       </c>
       <c r="B246" t="s">
         <v>4</v>
       </c>
       <c r="C246">
-        <v>120</v>
+        <v>289</v>
       </c>
       <c r="D246">
         <f t="shared" si="3"/>
-        <v>-53788</v>
+        <v>7011</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A247" s="2">
-        <v>45777</v>
+        <v>45779</v>
       </c>
       <c r="B247" t="s">
         <v>4</v>
       </c>
       <c r="C247">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="D247">
         <f t="shared" si="3"/>
-        <v>-53898</v>
+        <v>6811</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A248" s="2">
-        <v>45777</v>
+        <v>45779</v>
       </c>
       <c r="B248" t="s">
         <v>4</v>
       </c>
       <c r="C248">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="D248">
         <f t="shared" si="3"/>
-        <v>-53977</v>
+        <v>6611</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A249" s="2">
-        <v>45777</v>
+        <v>45779</v>
       </c>
       <c r="B249" t="s">
         <v>4</v>
       </c>
       <c r="C249">
-        <v>340</v>
+        <v>102</v>
       </c>
       <c r="D249">
         <f t="shared" si="3"/>
-        <v>-54317</v>
+        <v>6509</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A250" s="2">
-        <v>45777</v>
+        <v>45778</v>
       </c>
       <c r="B250" t="s">
         <v>4</v>
       </c>
       <c r="C250">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D250">
         <f t="shared" si="3"/>
-        <v>-54382</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A251" s="2">
-        <v>45776</v>
+        <v>45778</v>
       </c>
       <c r="B251" t="s">
         <v>4</v>
       </c>
       <c r="C251">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="D251">
         <f t="shared" si="3"/>
-        <v>-54507</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A252" s="2">
-        <v>45776</v>
+        <v>45778</v>
       </c>
       <c r="B252" t="s">
         <v>4</v>
       </c>
       <c r="C252">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="D252">
         <f t="shared" si="3"/>
-        <v>-54647</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A253" s="2">
-        <v>45775</v>
+        <v>45778</v>
       </c>
       <c r="B253" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C253">
-        <v>105</v>
+        <v>10000</v>
       </c>
       <c r="D253">
         <f t="shared" si="3"/>
-        <v>-54752</v>
+        <v>16212</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A254" s="2">
-        <v>45775</v>
+        <v>45777</v>
       </c>
       <c r="B254" t="s">
         <v>4</v>
       </c>
       <c r="C254">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="D254">
         <f t="shared" si="3"/>
-        <v>-54882</v>
+        <v>16102</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A255" s="2">
-        <v>45774</v>
+        <v>45777</v>
       </c>
       <c r="B255" t="s">
         <v>4</v>
       </c>
       <c r="C255">
-        <v>240</v>
+        <v>79</v>
       </c>
       <c r="D255">
         <f t="shared" si="3"/>
-        <v>-55122</v>
+        <v>16023</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A256" s="2">
-        <v>45774</v>
+        <v>45777</v>
       </c>
       <c r="B256" t="s">
         <v>4</v>
       </c>
       <c r="C256">
-        <v>200</v>
+        <v>340</v>
       </c>
       <c r="D256">
         <f t="shared" si="3"/>
-        <v>-55322</v>
+        <v>15683</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A257" s="2">
-        <v>45774</v>
+        <v>45777</v>
       </c>
       <c r="B257" t="s">
         <v>4</v>
       </c>
       <c r="C257">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="D257">
         <f t="shared" si="3"/>
-        <v>-55422</v>
+        <v>15618</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A258" s="2">
-        <v>45772</v>
+        <v>45776</v>
       </c>
       <c r="B258" t="s">
         <v>4</v>
       </c>
       <c r="C258">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="D258">
         <f t="shared" si="3"/>
-        <v>-55532</v>
+        <v>15493</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A259" s="2">
-        <v>45771</v>
+        <v>45776</v>
       </c>
       <c r="B259" t="s">
         <v>4</v>
       </c>
       <c r="C259">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="D259">
-        <f t="shared" ref="D259:D274" si="4">IF(B259="Income",D258+C259,D258-C259)</f>
-        <v>-55581</v>
+        <f t="shared" ref="D259:D322" si="4">IF(B259="Income",D258+C259,D258-C259)</f>
+        <v>15353</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A260" s="2">
-        <v>45771</v>
+        <v>45775</v>
       </c>
       <c r="B260" t="s">
         <v>4</v>
       </c>
       <c r="C260">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="D260">
         <f t="shared" si="4"/>
-        <v>-55706</v>
+        <v>15248</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A261" s="2">
-        <v>45771</v>
+        <v>45775</v>
       </c>
       <c r="B261" t="s">
         <v>4</v>
       </c>
       <c r="C261">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="D261">
         <f t="shared" si="4"/>
-        <v>-55815</v>
+        <v>15118</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A262" s="2">
-        <v>45771</v>
+        <v>45774</v>
       </c>
       <c r="B262" t="s">
         <v>4</v>
       </c>
       <c r="C262">
-        <v>406</v>
+        <v>240</v>
       </c>
       <c r="D262">
         <f t="shared" si="4"/>
-        <v>-56221</v>
+        <v>14878</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A263" s="2">
-        <v>45770</v>
+        <v>45774</v>
       </c>
       <c r="B263" t="s">
         <v>4</v>
       </c>
       <c r="C263">
-        <v>45</v>
+        <v>200</v>
       </c>
       <c r="D263">
         <f t="shared" si="4"/>
-        <v>-56266</v>
+        <v>14678</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A264" s="2">
-        <v>45770</v>
+        <v>45774</v>
       </c>
       <c r="B264" t="s">
         <v>4</v>
       </c>
       <c r="C264">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D264">
         <f t="shared" si="4"/>
-        <v>-56296</v>
+        <v>14578</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A265" s="2">
-        <v>45770</v>
+        <v>45772</v>
       </c>
       <c r="B265" t="s">
         <v>4</v>
       </c>
       <c r="C265">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="D265">
         <f t="shared" si="4"/>
-        <v>-56441</v>
+        <v>14468</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A266" s="2">
-        <v>45769</v>
+        <v>45771</v>
       </c>
       <c r="B266" t="s">
         <v>4</v>
       </c>
       <c r="C266">
-        <v>172</v>
+        <v>49</v>
       </c>
       <c r="D266">
         <f t="shared" si="4"/>
-        <v>-56613</v>
+        <v>14419</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A267" s="2">
-        <v>45769</v>
+        <v>45771</v>
       </c>
       <c r="B267" t="s">
         <v>4</v>
       </c>
       <c r="C267">
-        <v>180</v>
+        <v>125</v>
       </c>
       <c r="D267">
         <f t="shared" si="4"/>
-        <v>-56793</v>
+        <v>14294</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A268" s="2">
-        <v>45768</v>
+        <v>45771</v>
       </c>
       <c r="B268" t="s">
         <v>4</v>
       </c>
       <c r="C268">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D268">
         <f t="shared" si="4"/>
-        <v>-56911</v>
+        <v>14185</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A269" s="2">
-        <v>45768</v>
+        <v>45771</v>
       </c>
       <c r="B269" t="s">
         <v>4</v>
       </c>
       <c r="C269">
-        <v>110</v>
+        <v>406</v>
       </c>
       <c r="D269">
         <f t="shared" si="4"/>
-        <v>-57021</v>
+        <v>13779</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A270" s="2">
-        <v>45767</v>
+        <v>45770</v>
       </c>
       <c r="B270" t="s">
         <v>4</v>
       </c>
       <c r="C270">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="D270">
         <f t="shared" si="4"/>
-        <v>-57116</v>
+        <v>13734</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A271" s="2">
-        <v>45767</v>
+        <v>45770</v>
       </c>
       <c r="B271" t="s">
         <v>4</v>
       </c>
       <c r="C271">
-        <v>190</v>
+        <v>30</v>
       </c>
       <c r="D271">
         <f t="shared" si="4"/>
-        <v>-57306</v>
+        <v>13704</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A272" s="2">
-        <v>45766</v>
+        <v>45770</v>
       </c>
       <c r="B272" t="s">
         <v>4</v>
@@ -4526,652 +4530,787 @@
       </c>
       <c r="D272">
         <f t="shared" si="4"/>
-        <v>-57451</v>
+        <v>13559</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A273" s="2">
-        <v>45766</v>
+        <v>45769</v>
       </c>
       <c r="B273" t="s">
         <v>4</v>
       </c>
       <c r="C273">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="D273">
         <f t="shared" si="4"/>
-        <v>-57540</v>
+        <v>13387</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A274" s="2">
-        <v>45765</v>
+        <v>45769</v>
       </c>
       <c r="B274" t="s">
         <v>4</v>
       </c>
       <c r="C274">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D274">
         <f t="shared" si="4"/>
-        <v>-57723</v>
+        <v>13207</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A275" s="2">
-        <v>45765</v>
+        <v>45768</v>
       </c>
       <c r="B275" t="s">
         <v>4</v>
       </c>
       <c r="C275">
-        <v>228</v>
+        <v>118</v>
       </c>
       <c r="D275">
-        <f t="shared" ref="D275:D315" si="5">IF(B275="Income",D274+C275,D274-C275)</f>
-        <v>-57951</v>
+        <f t="shared" si="4"/>
+        <v>13089</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A276" s="2">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="B276" t="s">
         <v>4</v>
       </c>
       <c r="C276">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="D276">
-        <f t="shared" si="5"/>
-        <v>-58081</v>
+        <f t="shared" si="4"/>
+        <v>12979</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A277" s="2">
-        <v>45764</v>
+        <v>45767</v>
       </c>
       <c r="B277" t="s">
         <v>4</v>
       </c>
       <c r="C277">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="D277">
-        <f t="shared" si="5"/>
-        <v>-58241</v>
+        <f t="shared" si="4"/>
+        <v>12884</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A278" s="2">
-        <v>45763</v>
+        <v>45767</v>
       </c>
       <c r="B278" t="s">
         <v>4</v>
       </c>
       <c r="C278">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="D278">
-        <f t="shared" si="5"/>
-        <v>-58481</v>
+        <f t="shared" si="4"/>
+        <v>12694</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A279" s="2">
-        <v>45763</v>
+        <v>45766</v>
       </c>
       <c r="B279" t="s">
         <v>4</v>
       </c>
       <c r="C279">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="D279">
-        <f t="shared" si="5"/>
-        <v>-58641</v>
+        <f t="shared" si="4"/>
+        <v>12549</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A280" s="2">
-        <v>45763</v>
+        <v>45766</v>
       </c>
       <c r="B280" t="s">
         <v>4</v>
       </c>
       <c r="C280">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="D280">
-        <f t="shared" si="5"/>
-        <v>-58690</v>
+        <f t="shared" si="4"/>
+        <v>12460</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A281" s="2">
-        <v>45763</v>
+        <v>45765</v>
       </c>
       <c r="B281" t="s">
         <v>4</v>
       </c>
       <c r="C281">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="D281">
-        <f t="shared" si="5"/>
-        <v>-58851</v>
+        <f t="shared" si="4"/>
+        <v>12277</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A282" s="2">
-        <v>45762</v>
+        <v>45765</v>
       </c>
       <c r="B282" t="s">
         <v>4</v>
       </c>
       <c r="C282">
-        <v>108</v>
+        <v>228</v>
       </c>
       <c r="D282">
-        <f t="shared" si="5"/>
-        <v>-58959</v>
+        <f t="shared" si="4"/>
+        <v>12049</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A283" s="2">
-        <v>45762</v>
+        <v>45764</v>
       </c>
       <c r="B283" t="s">
         <v>4</v>
       </c>
       <c r="C283">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="D283">
-        <f t="shared" si="5"/>
-        <v>-59113</v>
+        <f t="shared" si="4"/>
+        <v>11919</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A284" s="2">
-        <v>45762</v>
+        <v>45764</v>
       </c>
       <c r="B284" t="s">
         <v>4</v>
       </c>
       <c r="C284">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="D284">
-        <f t="shared" si="5"/>
-        <v>-59198</v>
+        <f t="shared" si="4"/>
+        <v>11759</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A285" s="2">
-        <v>45761</v>
+        <v>45763</v>
       </c>
       <c r="B285" t="s">
         <v>4</v>
       </c>
       <c r="C285">
-        <v>141</v>
+        <v>240</v>
       </c>
       <c r="D285">
-        <f t="shared" si="5"/>
-        <v>-59339</v>
+        <f t="shared" si="4"/>
+        <v>11519</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A286" s="2">
-        <v>45761</v>
+        <v>45763</v>
       </c>
       <c r="B286" t="s">
         <v>4</v>
       </c>
       <c r="C286">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="D286">
-        <f t="shared" si="5"/>
-        <v>-59489</v>
+        <f t="shared" si="4"/>
+        <v>11359</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A287" s="2">
-        <v>45761</v>
+        <v>45763</v>
       </c>
       <c r="B287" t="s">
         <v>4</v>
       </c>
       <c r="C287">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="D287">
-        <f t="shared" si="5"/>
-        <v>-59579</v>
+        <f t="shared" si="4"/>
+        <v>11310</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A288" s="2">
-        <v>45760</v>
+        <v>45763</v>
       </c>
       <c r="B288" t="s">
         <v>4</v>
       </c>
       <c r="C288">
-        <v>50</v>
+        <v>161</v>
       </c>
       <c r="D288">
-        <f t="shared" si="5"/>
-        <v>-59629</v>
+        <f t="shared" si="4"/>
+        <v>11149</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A289" s="2">
-        <v>45760</v>
+        <v>45762</v>
       </c>
       <c r="B289" t="s">
         <v>4</v>
       </c>
       <c r="C289">
-        <v>297</v>
+        <v>108</v>
       </c>
       <c r="D289">
-        <f t="shared" si="5"/>
-        <v>-59926</v>
+        <f t="shared" si="4"/>
+        <v>11041</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A290" s="2">
-        <v>45760</v>
+        <v>45762</v>
       </c>
       <c r="B290" t="s">
         <v>4</v>
       </c>
       <c r="C290">
-        <v>30</v>
+        <v>154</v>
       </c>
       <c r="D290">
-        <f t="shared" si="5"/>
-        <v>-59956</v>
+        <f t="shared" si="4"/>
+        <v>10887</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A291" s="2">
-        <v>45759</v>
+        <v>45762</v>
       </c>
       <c r="B291" t="s">
         <v>4</v>
       </c>
       <c r="C291">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="D291">
-        <f t="shared" si="5"/>
-        <v>-59976</v>
+        <f t="shared" si="4"/>
+        <v>10802</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A292" s="2">
-        <v>45759</v>
+        <v>45761</v>
       </c>
       <c r="B292" t="s">
         <v>4</v>
       </c>
       <c r="C292">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="D292">
-        <f t="shared" si="5"/>
-        <v>-60140</v>
+        <f t="shared" si="4"/>
+        <v>10661</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A293" s="2">
-        <v>45759</v>
+        <v>45761</v>
       </c>
       <c r="B293" t="s">
         <v>4</v>
       </c>
       <c r="C293">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="D293">
-        <f t="shared" si="5"/>
-        <v>-60200</v>
+        <f t="shared" si="4"/>
+        <v>10511</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A294" s="2">
-        <v>45759</v>
+        <v>45761</v>
       </c>
       <c r="B294" t="s">
         <v>4</v>
       </c>
       <c r="C294">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D294">
-        <f t="shared" si="5"/>
-        <v>-60250</v>
+        <f t="shared" si="4"/>
+        <v>10421</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A295" s="2">
-        <v>45758</v>
+        <v>45760</v>
       </c>
       <c r="B295" t="s">
         <v>4</v>
       </c>
       <c r="C295">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D295">
-        <f t="shared" si="5"/>
-        <v>-60310</v>
+        <f t="shared" si="4"/>
+        <v>10371</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A296" s="2">
-        <v>45758</v>
+        <v>45760</v>
       </c>
       <c r="B296" t="s">
         <v>4</v>
       </c>
       <c r="C296">
-        <v>210</v>
+        <v>297</v>
       </c>
       <c r="D296">
-        <f t="shared" si="5"/>
-        <v>-60520</v>
+        <f t="shared" si="4"/>
+        <v>10074</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A297" s="2">
-        <v>45758</v>
+        <v>45760</v>
       </c>
       <c r="B297" t="s">
         <v>4</v>
       </c>
       <c r="C297">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="D297">
-        <f t="shared" si="5"/>
-        <v>-60620</v>
+        <f t="shared" si="4"/>
+        <v>10044</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A298" s="2">
-        <v>45757</v>
+        <v>45759</v>
       </c>
       <c r="B298" t="s">
         <v>4</v>
       </c>
       <c r="C298">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="D298">
-        <f t="shared" si="5"/>
-        <v>-60739</v>
+        <f t="shared" si="4"/>
+        <v>10024</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A299" s="2">
-        <v>45757</v>
+        <v>45759</v>
       </c>
       <c r="B299" t="s">
         <v>4</v>
       </c>
       <c r="C299">
-        <v>91</v>
+        <v>164</v>
       </c>
       <c r="D299">
-        <f t="shared" si="5"/>
-        <v>-60830</v>
+        <f t="shared" si="4"/>
+        <v>9860</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A300" s="2">
-        <v>45757</v>
+        <v>45759</v>
       </c>
       <c r="B300" t="s">
         <v>4</v>
       </c>
       <c r="C300">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="D300">
-        <f t="shared" si="5"/>
-        <v>-60967</v>
+        <f t="shared" si="4"/>
+        <v>9800</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A301" s="2">
-        <v>45756</v>
+        <v>45759</v>
       </c>
       <c r="B301" t="s">
         <v>4</v>
       </c>
       <c r="C301">
-        <v>139</v>
+        <v>50</v>
       </c>
       <c r="D301">
-        <f t="shared" si="5"/>
-        <v>-61106</v>
+        <f t="shared" si="4"/>
+        <v>9750</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A302" s="2">
-        <v>45756</v>
+        <v>45758</v>
       </c>
       <c r="B302" t="s">
         <v>4</v>
       </c>
       <c r="C302">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D302">
-        <f t="shared" si="5"/>
-        <v>-61157</v>
+        <f t="shared" si="4"/>
+        <v>9690</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A303" s="2">
-        <v>45755</v>
+        <v>45758</v>
       </c>
       <c r="B303" t="s">
         <v>4</v>
       </c>
       <c r="C303">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="D303">
-        <f t="shared" si="5"/>
-        <v>-61219</v>
+        <f t="shared" si="4"/>
+        <v>9480</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A304" s="2">
-        <v>45755</v>
+        <v>45758</v>
       </c>
       <c r="B304" t="s">
         <v>4</v>
       </c>
       <c r="C304">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="D304">
-        <f t="shared" si="5"/>
-        <v>-61284</v>
+        <f t="shared" si="4"/>
+        <v>9380</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A305" s="2">
-        <v>45752</v>
+        <v>45757</v>
       </c>
       <c r="B305" t="s">
         <v>4</v>
       </c>
       <c r="C305">
-        <v>350</v>
+        <v>119</v>
       </c>
       <c r="D305">
-        <f t="shared" si="5"/>
-        <v>-61634</v>
+        <f t="shared" si="4"/>
+        <v>9261</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A306" s="2">
-        <v>45749</v>
+        <v>45757</v>
       </c>
       <c r="B306" t="s">
         <v>4</v>
       </c>
       <c r="C306">
-        <v>500</v>
+        <v>91</v>
       </c>
       <c r="D306">
-        <f t="shared" si="5"/>
-        <v>-62134</v>
+        <f t="shared" si="4"/>
+        <v>9170</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A307" s="2">
-        <v>45748</v>
+        <v>45757</v>
       </c>
       <c r="B307" t="s">
         <v>4</v>
       </c>
       <c r="C307">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="D307">
-        <f t="shared" si="5"/>
-        <v>-62214</v>
+        <f t="shared" si="4"/>
+        <v>9033</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A308" s="2">
-        <v>45748</v>
+        <v>45756</v>
       </c>
       <c r="B308" t="s">
         <v>4</v>
       </c>
       <c r="C308">
-        <v>704</v>
+        <v>139</v>
       </c>
       <c r="D308">
-        <f t="shared" si="5"/>
-        <v>-62918</v>
+        <f t="shared" si="4"/>
+        <v>8894</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A309" s="2">
-        <v>45673</v>
+        <v>45756</v>
       </c>
       <c r="B309" t="s">
         <v>4</v>
       </c>
       <c r="C309">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="D309">
-        <f t="shared" si="5"/>
-        <v>-63053</v>
+        <f t="shared" si="4"/>
+        <v>8843</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A310" s="2">
-        <v>45672</v>
+        <v>45755</v>
       </c>
       <c r="B310" t="s">
         <v>4</v>
       </c>
       <c r="C310">
-        <v>160</v>
+        <v>62</v>
       </c>
       <c r="D310">
-        <f t="shared" si="5"/>
-        <v>-63213</v>
+        <f t="shared" si="4"/>
+        <v>8781</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A311" s="2">
-        <v>45672</v>
+        <v>45755</v>
       </c>
       <c r="B311" t="s">
         <v>4</v>
       </c>
       <c r="C311">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="D311">
-        <f t="shared" si="5"/>
-        <v>-63343</v>
+        <f t="shared" si="4"/>
+        <v>8716</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A312" s="2">
-        <v>45666</v>
+        <v>45752</v>
       </c>
       <c r="B312" t="s">
         <v>4</v>
       </c>
       <c r="C312">
-        <v>603</v>
+        <v>350</v>
       </c>
       <c r="D312">
-        <f t="shared" si="5"/>
-        <v>-63946</v>
+        <f t="shared" si="4"/>
+        <v>8366</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A313" s="2">
-        <v>45665</v>
+        <v>45749</v>
       </c>
       <c r="B313" t="s">
         <v>4</v>
       </c>
       <c r="C313">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="D313">
-        <f t="shared" si="5"/>
-        <v>-64016</v>
+        <f t="shared" si="4"/>
+        <v>7866</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A314" s="2">
-        <v>45665</v>
+        <v>45748</v>
       </c>
       <c r="B314" t="s">
         <v>4</v>
       </c>
       <c r="C314">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="D314">
-        <f t="shared" si="5"/>
-        <v>-64196</v>
+        <f t="shared" si="4"/>
+        <v>7786</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A315" s="2">
+        <v>45748</v>
+      </c>
+      <c r="B315" t="s">
+        <v>4</v>
+      </c>
+      <c r="C315">
+        <v>704</v>
+      </c>
+      <c r="D315">
+        <f t="shared" si="4"/>
+        <v>7082</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A316" s="2">
+        <v>45748</v>
+      </c>
+      <c r="B316" t="s">
+        <v>5</v>
+      </c>
+      <c r="C316">
+        <v>10000</v>
+      </c>
+      <c r="D316">
+        <f t="shared" si="4"/>
+        <v>17082</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A317" s="2">
+        <v>45673</v>
+      </c>
+      <c r="B317" t="s">
+        <v>4</v>
+      </c>
+      <c r="C317">
+        <v>135</v>
+      </c>
+      <c r="D317">
+        <f t="shared" si="4"/>
+        <v>16947</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A318" s="2">
+        <v>45672</v>
+      </c>
+      <c r="B318" t="s">
+        <v>4</v>
+      </c>
+      <c r="C318">
+        <v>160</v>
+      </c>
+      <c r="D318">
+        <f t="shared" si="4"/>
+        <v>16787</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A319" s="2">
+        <v>45672</v>
+      </c>
+      <c r="B319" t="s">
+        <v>4</v>
+      </c>
+      <c r="C319">
+        <v>130</v>
+      </c>
+      <c r="D319">
+        <f t="shared" si="4"/>
+        <v>16657</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A320" s="2">
+        <v>45666</v>
+      </c>
+      <c r="B320" t="s">
+        <v>4</v>
+      </c>
+      <c r="C320">
+        <v>603</v>
+      </c>
+      <c r="D320">
+        <f t="shared" si="4"/>
+        <v>16054</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A321" s="2">
         <v>45665</v>
       </c>
-      <c r="B315" t="s">
-        <v>4</v>
-      </c>
-      <c r="C315">
+      <c r="B321" t="s">
+        <v>4</v>
+      </c>
+      <c r="C321">
+        <v>70</v>
+      </c>
+      <c r="D321">
+        <f t="shared" si="4"/>
+        <v>15984</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A322" s="2">
+        <v>45665</v>
+      </c>
+      <c r="B322" t="s">
+        <v>4</v>
+      </c>
+      <c r="C322">
+        <v>180</v>
+      </c>
+      <c r="D322">
+        <f t="shared" si="4"/>
+        <v>15804</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A323" s="2">
+        <v>45665</v>
+      </c>
+      <c r="B323" t="s">
+        <v>4</v>
+      </c>
+      <c r="C323">
         <v>110</v>
       </c>
-      <c r="D315">
+      <c r="D323">
+        <f t="shared" ref="D323:D324" si="5">IF(B323="Income",D322+C323,D322-C323)</f>
+        <v>15694</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A324" s="2">
+        <v>45658</v>
+      </c>
+      <c r="B324" t="s">
+        <v>5</v>
+      </c>
+      <c r="C324">
+        <v>10000</v>
+      </c>
+      <c r="D324">
         <f t="shared" si="5"/>
-        <v>-64306</v>
+        <v>25694</v>
       </c>
     </row>
   </sheetData>
